--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/77.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/77.xlsx
@@ -426,13 +426,13 @@
         <v>2.828159137149092</v>
       </c>
       <c r="E2">
-        <v>-7.521521166533597</v>
+        <v>-3.101413541866792</v>
       </c>
       <c r="F2">
-        <v>-3.971171110348462</v>
+        <v>-2.622608031041131</v>
       </c>
       <c r="G2">
-        <v>-11.36116291856306</v>
+        <v>-7.910889543154188</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.313096045473155</v>
       </c>
       <c r="E3">
-        <v>-7.113143380521885</v>
+        <v>-4.003748215687172</v>
       </c>
       <c r="F3">
-        <v>-3.686740393821015</v>
+        <v>-2.352611616507466</v>
       </c>
       <c r="G3">
-        <v>-11.63329430981716</v>
+        <v>-7.798888326444103</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.641671966606925</v>
       </c>
       <c r="E4">
-        <v>-7.917083371103604</v>
+        <v>-4.079034096064691</v>
       </c>
       <c r="F4">
-        <v>-3.898715470360395</v>
+        <v>-2.239139364569781</v>
       </c>
       <c r="G4">
-        <v>-11.73237407602615</v>
+        <v>-7.29284849388186</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.751799450882348</v>
       </c>
       <c r="E5">
-        <v>-8.319021667076409</v>
+        <v>-4.724518252644017</v>
       </c>
       <c r="F5">
-        <v>-3.924344329435609</v>
+        <v>-2.436898828109718</v>
       </c>
       <c r="G5">
-        <v>-11.40618127835864</v>
+        <v>-7.333991731015737</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.690028461623057</v>
       </c>
       <c r="E6">
-        <v>-8.839470127829948</v>
+        <v>-5.577220851340329</v>
       </c>
       <c r="F6">
-        <v>-3.50314021429713</v>
+        <v>-2.374995760465914</v>
       </c>
       <c r="G6">
-        <v>-11.28085830211721</v>
+        <v>-7.250845576699408</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.483989335246833</v>
       </c>
       <c r="E7">
-        <v>-9.669457900903787</v>
+        <v>-6.303891489929169</v>
       </c>
       <c r="F7">
-        <v>-3.616730922773415</v>
+        <v>-2.143245897286905</v>
       </c>
       <c r="G7">
-        <v>-11.67665237150366</v>
+        <v>-6.839432892689992</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.178238072225764</v>
       </c>
       <c r="E8">
-        <v>-10.23657681478038</v>
+        <v>-6.967897105199865</v>
       </c>
       <c r="F8">
-        <v>-3.587241043233753</v>
+        <v>-1.813250003401069</v>
       </c>
       <c r="G8">
-        <v>-11.88719195286543</v>
+        <v>-7.140773718266276</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>2.811479110930132</v>
       </c>
       <c r="E9">
-        <v>-11.51007427521743</v>
+        <v>-7.439537673098734</v>
       </c>
       <c r="F9">
-        <v>-3.272247711380019</v>
+        <v>-1.997457376231206</v>
       </c>
       <c r="G9">
-        <v>-11.64667841255814</v>
+        <v>-7.090849932239324</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.42877965958125</v>
       </c>
       <c r="E10">
-        <v>-11.29516195576141</v>
+        <v>-8.248712579633318</v>
       </c>
       <c r="F10">
-        <v>-3.332319258696233</v>
+        <v>-2.016571954050804</v>
       </c>
       <c r="G10">
-        <v>-11.36583209684215</v>
+        <v>-6.802368213954504</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.069068828607229</v>
       </c>
       <c r="E11">
-        <v>-11.30222637521338</v>
+        <v>-8.61969422728969</v>
       </c>
       <c r="F11">
-        <v>-3.112123464051471</v>
+        <v>-1.639825489053173</v>
       </c>
       <c r="G11">
-        <v>-10.52082895230303</v>
+        <v>-6.098706969310026</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.767497559742606</v>
       </c>
       <c r="E12">
-        <v>-12.96685719264094</v>
+        <v>-9.431482063326701</v>
       </c>
       <c r="F12">
-        <v>-2.891860571647082</v>
+        <v>-1.679376719067238</v>
       </c>
       <c r="G12">
-        <v>-10.35591803794689</v>
+        <v>-5.562151776244947</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.545286727336772</v>
       </c>
       <c r="E13">
-        <v>-12.86654243642303</v>
+        <v>-10.34606625933783</v>
       </c>
       <c r="F13">
-        <v>-2.562043605120251</v>
+        <v>-1.184027922806384</v>
       </c>
       <c r="G13">
-        <v>-9.779194130551094</v>
+        <v>-6.111083737032251</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.411849134726741</v>
       </c>
       <c r="E14">
-        <v>-14.14353135032</v>
+        <v>-11.05153911109676</v>
       </c>
       <c r="F14">
-        <v>-2.470835383867609</v>
+        <v>-0.9130051610606501</v>
       </c>
       <c r="G14">
-        <v>-9.974653217625656</v>
+        <v>-5.135064696846064</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.362053444261454</v>
       </c>
       <c r="E15">
-        <v>-14.34829535952483</v>
+        <v>-12.37411164435495</v>
       </c>
       <c r="F15">
-        <v>-1.9947925182964</v>
+        <v>-0.3657367810945314</v>
       </c>
       <c r="G15">
-        <v>-8.940825616005171</v>
+        <v>-5.607744349813432</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.379096273788897</v>
       </c>
       <c r="E16">
-        <v>-15.04092545899801</v>
+        <v>-11.87453492030276</v>
       </c>
       <c r="F16">
-        <v>-1.907190180348144</v>
+        <v>-0.6250803908281951</v>
       </c>
       <c r="G16">
-        <v>-8.94355559234263</v>
+        <v>-5.276281910321446</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.437427348006138</v>
       </c>
       <c r="E17">
-        <v>-16.10612670050426</v>
+        <v>-13.34553271763635</v>
       </c>
       <c r="F17">
-        <v>-1.583379705859012</v>
+        <v>0.1539154863970572</v>
       </c>
       <c r="G17">
-        <v>-8.427143818430983</v>
+        <v>-3.469769287332003</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.508561786073581</v>
       </c>
       <c r="E18">
-        <v>-16.92128824967698</v>
+        <v>-15.09292139755408</v>
       </c>
       <c r="F18">
-        <v>-1.06120257452369</v>
+        <v>0.3893234200268291</v>
       </c>
       <c r="G18">
-        <v>-8.955942203729533</v>
+        <v>-4.555853623508204</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.566454345912859</v>
       </c>
       <c r="E19">
-        <v>-17.50553838072459</v>
+        <v>-16.81012326973669</v>
       </c>
       <c r="F19">
-        <v>-0.7681833447640181</v>
+        <v>0.5935690003306864</v>
       </c>
       <c r="G19">
-        <v>-8.176415835409133</v>
+        <v>-2.809298762074496</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.592732639026669</v>
       </c>
       <c r="E20">
-        <v>-18.39327325434424</v>
+        <v>-16.69961491852751</v>
       </c>
       <c r="F20">
-        <v>-0.3604186623685586</v>
+        <v>0.9552938508459521</v>
       </c>
       <c r="G20">
-        <v>-7.686227584200569</v>
+        <v>-2.718943763992066</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.580130498562904</v>
       </c>
       <c r="E21">
-        <v>-19.19574601934747</v>
+        <v>-17.50792488652663</v>
       </c>
       <c r="F21">
-        <v>0.1910619658407954</v>
+        <v>0.9971396585657719</v>
       </c>
       <c r="G21">
-        <v>-7.513717360712763</v>
+        <v>-3.396105863322469</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.534230725092984</v>
       </c>
       <c r="E22">
-        <v>-19.46118252330707</v>
+        <v>-15.95830825194588</v>
       </c>
       <c r="F22">
-        <v>0.006956482201202496</v>
+        <v>1.417610668552773</v>
       </c>
       <c r="G22">
-        <v>-7.309024916169922</v>
+        <v>-2.899246888683554</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.471904172055847</v>
       </c>
       <c r="E23">
-        <v>-21.11423403269702</v>
+        <v>-16.96771869367763</v>
       </c>
       <c r="F23">
-        <v>0.326427968234471</v>
+        <v>1.912550251316644</v>
       </c>
       <c r="G23">
-        <v>-7.671655679255074</v>
+        <v>-3.182705056760863</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.415888549990856</v>
       </c>
       <c r="E24">
-        <v>-21.50324353537793</v>
+        <v>-19.02137259920812</v>
       </c>
       <c r="F24">
-        <v>0.5110354425201604</v>
+        <v>1.431336716417161</v>
       </c>
       <c r="G24">
-        <v>-7.583364569533535</v>
+        <v>-2.912791771280941</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.390623220709949</v>
       </c>
       <c r="E25">
-        <v>-20.98116029550762</v>
+        <v>-18.25253281065985</v>
       </c>
       <c r="F25">
-        <v>0.581469037677994</v>
+        <v>2.049260694005063</v>
       </c>
       <c r="G25">
-        <v>-7.805611549419405</v>
+        <v>-2.119133181704013</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.417670474760572</v>
       </c>
       <c r="E26">
-        <v>-21.25927199821469</v>
+        <v>-18.78617271619774</v>
       </c>
       <c r="F26">
-        <v>0.4800263371637637</v>
+        <v>2.399726374781478</v>
       </c>
       <c r="G26">
-        <v>-7.580585374872686</v>
+        <v>-3.045523745803599</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.513046437680888</v>
       </c>
       <c r="E27">
-        <v>-21.53305900824443</v>
+        <v>-18.9069425895083</v>
       </c>
       <c r="F27">
-        <v>0.4083584745757589</v>
+        <v>1.846438248899215</v>
       </c>
       <c r="G27">
-        <v>-7.637330820521723</v>
+        <v>-3.257024725082287</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.684622580897391</v>
       </c>
       <c r="E28">
-        <v>-21.64228580130944</v>
+        <v>-18.60119360993242</v>
       </c>
       <c r="F28">
-        <v>0.380035764706641</v>
+        <v>1.977487628756903</v>
       </c>
       <c r="G28">
-        <v>-7.382002564873533</v>
+        <v>-3.978922999154159</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.928865998346441</v>
       </c>
       <c r="E29">
-        <v>-21.07086483712556</v>
+        <v>-19.01563049416639</v>
       </c>
       <c r="F29">
-        <v>0.5993692288850885</v>
+        <v>1.434148195382262</v>
       </c>
       <c r="G29">
-        <v>-7.439305818187675</v>
+        <v>-3.707677537721102</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.231406609752088</v>
       </c>
       <c r="E30">
-        <v>-20.41427233380542</v>
+        <v>-17.20487940593333</v>
       </c>
       <c r="F30">
-        <v>0.2536583770007428</v>
+        <v>1.385292742699953</v>
       </c>
       <c r="G30">
-        <v>-7.445425296396039</v>
+        <v>-2.838301479438427</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.570002224221625</v>
       </c>
       <c r="E31">
-        <v>-21.1179428529093</v>
+        <v>-18.58918409686407</v>
       </c>
       <c r="F31">
-        <v>0.4980632089923202</v>
+        <v>1.462292806259778</v>
       </c>
       <c r="G31">
-        <v>-7.533168442117151</v>
+        <v>-3.120342159802057</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.917147868547223</v>
       </c>
       <c r="E32">
-        <v>-20.47765738449078</v>
+        <v>-17.84305460546427</v>
       </c>
       <c r="F32">
-        <v>0.03327205785333719</v>
+        <v>1.425669026647207</v>
       </c>
       <c r="G32">
-        <v>-7.718623084656966</v>
+        <v>-2.225543196876805</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.24089998052535</v>
       </c>
       <c r="E33">
-        <v>-19.77774097033926</v>
+        <v>-17.68605241161834</v>
       </c>
       <c r="F33">
-        <v>0.1585502020157204</v>
+        <v>1.456959776920555</v>
       </c>
       <c r="G33">
-        <v>-7.439033476798241</v>
+        <v>-3.721107577563909</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.508265852271384</v>
       </c>
       <c r="E34">
-        <v>-19.95671984854441</v>
+        <v>-17.48333980113899</v>
       </c>
       <c r="F34">
-        <v>-0.0005195336090630422</v>
+        <v>1.539723620869059</v>
       </c>
       <c r="G34">
-        <v>-7.339143248864065</v>
+        <v>-3.65734359899922</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.690069353429952</v>
       </c>
       <c r="E35">
-        <v>-19.86170340691547</v>
+        <v>-15.87195025261961</v>
       </c>
       <c r="F35">
-        <v>0.05649202452121013</v>
+        <v>1.167450339846545</v>
       </c>
       <c r="G35">
-        <v>-7.154298913534307</v>
+        <v>-3.221699093773305</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.764073437701203</v>
       </c>
       <c r="E36">
-        <v>-19.67566010925835</v>
+        <v>-17.05178528515602</v>
       </c>
       <c r="F36">
-        <v>0.1130703464998192</v>
+        <v>1.32858602377391</v>
       </c>
       <c r="G36">
-        <v>-7.094232871667112</v>
+        <v>-2.628093301454161</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.717501229658243</v>
       </c>
       <c r="E37">
-        <v>-18.95363115652738</v>
+        <v>-16.51117605812033</v>
       </c>
       <c r="F37">
-        <v>0.05545739363511355</v>
+        <v>1.537768673798452</v>
       </c>
       <c r="G37">
-        <v>-6.668868433586937</v>
+        <v>-3.231460727912653</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.549557844352365</v>
       </c>
       <c r="E38">
-        <v>-19.10235982836129</v>
+        <v>-16.65238746310152</v>
       </c>
       <c r="F38">
-        <v>0.2752920200922547</v>
+        <v>1.219773338476973</v>
       </c>
       <c r="G38">
-        <v>-7.156001867523659</v>
+        <v>-1.997931419741244</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.271733757492466</v>
       </c>
       <c r="E39">
-        <v>-18.25799867878711</v>
+        <v>-14.92116543539116</v>
       </c>
       <c r="F39">
-        <v>0.09951577068781085</v>
+        <v>1.223399930966429</v>
       </c>
       <c r="G39">
-        <v>-6.508039358850754</v>
+        <v>-2.287863437955338</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.905146531875026</v>
       </c>
       <c r="E40">
-        <v>-17.9616191119331</v>
+        <v>-15.41643558066205</v>
       </c>
       <c r="F40">
-        <v>0.1012097820265358</v>
+        <v>1.69454051824787</v>
       </c>
       <c r="G40">
-        <v>-6.208624610329864</v>
+        <v>-2.84590735101322</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.477457252338546</v>
       </c>
       <c r="E41">
-        <v>-17.69013256669925</v>
+        <v>-14.49293934780383</v>
       </c>
       <c r="F41">
-        <v>-0.2048123308548799</v>
+        <v>1.420693852025993</v>
       </c>
       <c r="G41">
-        <v>-6.087668939984054</v>
+        <v>-2.482029723735479</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.017859823701813</v>
       </c>
       <c r="E42">
-        <v>-16.88093048932062</v>
+        <v>-14.89693357097612</v>
       </c>
       <c r="F42">
-        <v>0.09791702160040781</v>
+        <v>1.386288440318118</v>
       </c>
       <c r="G42">
-        <v>-6.123595034838414</v>
+        <v>-2.362055138635943</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.553364674676889</v>
       </c>
       <c r="E43">
-        <v>-17.05097015983464</v>
+        <v>-13.71259270680207</v>
       </c>
       <c r="F43">
-        <v>0.09713918460917907</v>
+        <v>1.357565628993448</v>
       </c>
       <c r="G43">
-        <v>-6.246322564826325</v>
+        <v>-2.410079097379976</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.105235023239853</v>
       </c>
       <c r="E44">
-        <v>-16.21178505605122</v>
+        <v>-13.60935708484921</v>
       </c>
       <c r="F44">
-        <v>-0.252706048982539</v>
+        <v>1.177236672343218</v>
       </c>
       <c r="G44">
-        <v>-5.996660978811295</v>
+        <v>-1.172047953229009</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.6882580871233487</v>
       </c>
       <c r="E45">
-        <v>-15.89764934261314</v>
+        <v>-13.39969779524209</v>
       </c>
       <c r="F45">
-        <v>0.02562539835809495</v>
+        <v>1.399358421199489</v>
       </c>
       <c r="G45">
-        <v>-5.922607089436188</v>
+        <v>-1.679465898846218</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.3117426698693088</v>
       </c>
       <c r="E46">
-        <v>-16.07173746889001</v>
+        <v>-13.1141910944805</v>
       </c>
       <c r="F46">
-        <v>-0.3952523400236806</v>
+        <v>1.134328897613009</v>
       </c>
       <c r="G46">
-        <v>-5.533244214306239</v>
+        <v>-0.796649957056058</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.01993389697753395</v>
       </c>
       <c r="E47">
-        <v>-15.49163994850744</v>
+        <v>-13.22533343205075</v>
       </c>
       <c r="F47">
-        <v>-0.1036761262796855</v>
+        <v>1.198986286871122</v>
       </c>
       <c r="G47">
-        <v>-5.290768503506394</v>
+        <v>-1.466990396764376</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.3044237716028034</v>
       </c>
       <c r="E48">
-        <v>-15.45920248919049</v>
+        <v>-12.75177279117263</v>
       </c>
       <c r="F48">
-        <v>-0.1403554065082448</v>
+        <v>0.933917001649308</v>
       </c>
       <c r="G48">
-        <v>-5.618237696360536</v>
+        <v>-0.7715650182341032</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.5408715083717808</v>
       </c>
       <c r="E49">
-        <v>-14.1776534019678</v>
+        <v>-12.13844985699578</v>
       </c>
       <c r="F49">
-        <v>-0.3197888979960485</v>
+        <v>1.02728229161884</v>
       </c>
       <c r="G49">
-        <v>-4.94859943806594</v>
+        <v>-1.274746906818069</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.7287016751263513</v>
       </c>
       <c r="E50">
-        <v>-13.79982470161183</v>
+        <v>-9.927150714310269</v>
       </c>
       <c r="F50">
-        <v>-0.2710577004241592</v>
+        <v>0.9363789095704282</v>
       </c>
       <c r="G50">
-        <v>-5.173894672780532</v>
+        <v>-1.938531465850616</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8694521754683617</v>
       </c>
       <c r="E51">
-        <v>-14.06184673616964</v>
+        <v>-10.27118341314699</v>
       </c>
       <c r="F51">
-        <v>-0.4571255864409841</v>
+        <v>0.954372706294039</v>
       </c>
       <c r="G51">
-        <v>-5.568136724369375</v>
+        <v>-0.7654521024688576</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9640665409539493</v>
       </c>
       <c r="E52">
-        <v>-12.98928219592693</v>
+        <v>-10.68833738178557</v>
       </c>
       <c r="F52">
-        <v>-0.4618439671673301</v>
+        <v>0.7679983243381783</v>
       </c>
       <c r="G52">
-        <v>-4.601593852046864</v>
+        <v>-0.2057478913018969</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.013688635408262</v>
       </c>
       <c r="E53">
-        <v>-12.91556769603007</v>
+        <v>-10.10261096821146</v>
       </c>
       <c r="F53">
-        <v>-0.5623588961904249</v>
+        <v>1.116509058043986</v>
       </c>
       <c r="G53">
-        <v>-5.474028008822941</v>
+        <v>-1.257707523259873</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.019751716334862</v>
       </c>
       <c r="E54">
-        <v>-12.56523588984867</v>
+        <v>-9.28600483583029</v>
       </c>
       <c r="F54">
-        <v>-0.4385395070243716</v>
+        <v>0.440683855735204</v>
       </c>
       <c r="G54">
-        <v>-5.121204816978969</v>
+        <v>-1.117783111078912</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.9857262216359163</v>
       </c>
       <c r="E55">
-        <v>-11.93248580217892</v>
+        <v>-9.42668188087857</v>
       </c>
       <c r="F55">
-        <v>-0.4760438411861193</v>
+        <v>0.5899208702887574</v>
       </c>
       <c r="G55">
-        <v>-5.509583325641084</v>
+        <v>-1.448668055576436</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.9158207511757216</v>
       </c>
       <c r="E56">
-        <v>-12.273778774241</v>
+        <v>-8.0604865575045</v>
       </c>
       <c r="F56">
-        <v>-0.4887509971450636</v>
+        <v>0.9416655503350947</v>
       </c>
       <c r="G56">
-        <v>-5.447555113281341</v>
+        <v>-1.04399500065012</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.8142915069894721</v>
       </c>
       <c r="E57">
-        <v>-11.52106035316004</v>
+        <v>-9.121503489027658</v>
       </c>
       <c r="F57">
-        <v>-0.4679813412546717</v>
+        <v>0.9000152373223355</v>
       </c>
       <c r="G57">
-        <v>-5.895281076289132</v>
+        <v>-1.175017458740306</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6848971122654287</v>
       </c>
       <c r="E58">
-        <v>-10.64568821358133</v>
+        <v>-8.024544059305621</v>
       </c>
       <c r="F58">
-        <v>-0.5449606956294269</v>
+        <v>0.4965721476672811</v>
       </c>
       <c r="G58">
-        <v>-5.821817806794724</v>
+        <v>-2.019823729985859</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.5307432357100468</v>
       </c>
       <c r="E59">
-        <v>-10.53651123373041</v>
+        <v>-7.710181922167153</v>
       </c>
       <c r="F59">
-        <v>-0.3658262447740338</v>
+        <v>0.9372056202384221</v>
       </c>
       <c r="G59">
-        <v>-5.674671425961426</v>
+        <v>-1.86104213750277</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.3564273998601113</v>
       </c>
       <c r="E60">
-        <v>-11.14798202203812</v>
+        <v>-7.453277063238006</v>
       </c>
       <c r="F60">
-        <v>-0.8055982152462634</v>
+        <v>0.8828614051451633</v>
       </c>
       <c r="G60">
-        <v>-6.30177520918094</v>
+        <v>-1.661054964676174</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.1680226096328544</v>
       </c>
       <c r="E61">
-        <v>-10.61537913704799</v>
+        <v>-6.331252529883513</v>
       </c>
       <c r="F61">
-        <v>-0.3683469667807527</v>
+        <v>1.113068019852757</v>
       </c>
       <c r="G61">
-        <v>-5.977935047371544</v>
+        <v>-2.540176250990399</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.02727528043745004</v>
       </c>
       <c r="E62">
-        <v>-10.8832429030757</v>
+        <v>-7.396811520836364</v>
       </c>
       <c r="F62">
-        <v>-0.4753811472638796</v>
+        <v>1.301592843586285</v>
       </c>
       <c r="G62">
-        <v>-5.939029603341208</v>
+        <v>-2.487000774398038</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.2214588011858367</v>
       </c>
       <c r="E63">
-        <v>-9.87170860703436</v>
+        <v>-5.178950619313738</v>
       </c>
       <c r="F63">
-        <v>-0.5363870930104521</v>
+        <v>0.7862124667909338</v>
       </c>
       <c r="G63">
-        <v>-6.633313116768794</v>
+        <v>-2.774580156754011</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.4057393413288136</v>
       </c>
       <c r="E64">
-        <v>-9.719588108168697</v>
+        <v>-6.860382075309756</v>
       </c>
       <c r="F64">
-        <v>-0.5856260798002575</v>
+        <v>0.7036466026516986</v>
       </c>
       <c r="G64">
-        <v>-6.649384539966954</v>
+        <v>-4.297053835450122</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.5713904166992868</v>
       </c>
       <c r="E65">
-        <v>-9.5475513806173</v>
+        <v>-7.26045916846541</v>
       </c>
       <c r="F65">
-        <v>-0.688261629374519</v>
+        <v>0.7688863341939793</v>
       </c>
       <c r="G65">
-        <v>-7.131336925061313</v>
+        <v>-4.294822604789699</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.7111720099520989</v>
       </c>
       <c r="E66">
-        <v>-9.007032723061766</v>
+        <v>-6.696573585030296</v>
       </c>
       <c r="F66">
-        <v>-0.6413536684561914</v>
+        <v>0.6936250138126303</v>
       </c>
       <c r="G66">
-        <v>-7.090259312358625</v>
+        <v>-3.520247599802501</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.8199152408692438</v>
       </c>
       <c r="E67">
-        <v>-8.998125214688679</v>
+        <v>-6.699435580603144</v>
       </c>
       <c r="F67">
-        <v>-0.4574925532004243</v>
+        <v>0.726278428463584</v>
       </c>
       <c r="G67">
-        <v>-6.834048408110943</v>
+        <v>-4.202462780334449</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.8952632861191278</v>
       </c>
       <c r="E68">
-        <v>-8.855202046532595</v>
+        <v>-6.470086486010671</v>
       </c>
       <c r="F68">
-        <v>-0.499967091778969</v>
+        <v>0.5937827191206086</v>
       </c>
       <c r="G68">
-        <v>-7.467826195982369</v>
+        <v>-3.974670536013118</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.9372416803845927</v>
       </c>
       <c r="E69">
-        <v>-9.587841213863543</v>
+        <v>-6.203282382900757</v>
       </c>
       <c r="F69">
-        <v>-0.7562084655891484</v>
+        <v>0.8152765654855573</v>
       </c>
       <c r="G69">
-        <v>-6.907806987545701</v>
+        <v>-4.442950070869271</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.9479122447012657</v>
       </c>
       <c r="E70">
-        <v>-9.790603637556984</v>
+        <v>-6.511381640486618</v>
       </c>
       <c r="F70">
-        <v>-0.6142884203045231</v>
+        <v>0.349949460636963</v>
       </c>
       <c r="G70">
-        <v>-7.119206248956046</v>
+        <v>-4.331962751621053</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.9304471204237674</v>
       </c>
       <c r="E71">
-        <v>-9.543548209594519</v>
+        <v>-6.773168194396033</v>
       </c>
       <c r="F71">
-        <v>-0.8284512151546961</v>
+        <v>0.3452252813387974</v>
       </c>
       <c r="G71">
-        <v>-7.298810473455371</v>
+        <v>-3.948489669190309</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.8886041622151875</v>
       </c>
       <c r="E72">
-        <v>-9.842835056761453</v>
+        <v>-7.124355882164877</v>
       </c>
       <c r="F72">
-        <v>-0.8584058088073291</v>
+        <v>0.1797837436516802</v>
       </c>
       <c r="G72">
-        <v>-7.31111177308173</v>
+        <v>-4.299143973583488</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.8268317056676888</v>
       </c>
       <c r="E73">
-        <v>-10.24271742553478</v>
+        <v>-5.974739356681649</v>
       </c>
       <c r="F73">
-        <v>-0.9783078485255435</v>
+        <v>0.4828767493967969</v>
       </c>
       <c r="G73">
-        <v>-7.378189785421458</v>
+        <v>-4.679680362718529</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.7503712925694495</v>
       </c>
       <c r="E74">
-        <v>-9.78676349159848</v>
+        <v>-6.599695940584205</v>
       </c>
       <c r="F74">
-        <v>-0.9825316939124181</v>
+        <v>0.4872033123416187</v>
       </c>
       <c r="G74">
-        <v>-7.093399441391013</v>
+        <v>-3.607439500301625</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.66483994782251</v>
       </c>
       <c r="E75">
-        <v>-10.26910937205148</v>
+        <v>-6.426119531870199</v>
       </c>
       <c r="F75">
-        <v>-0.8676661280032247</v>
+        <v>0.3900250472170003</v>
       </c>
       <c r="G75">
-        <v>-6.864649080374325</v>
+        <v>-3.521405871012985</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.5749843421448971</v>
       </c>
       <c r="E76">
-        <v>-10.44763993132988</v>
+        <v>-7.926706378369903</v>
       </c>
       <c r="F76">
-        <v>-0.8857079700361979</v>
+        <v>-0.01506815030443076</v>
       </c>
       <c r="G76">
-        <v>-6.767029457759285</v>
+        <v>-3.692488763122432</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.4845653248339998</v>
       </c>
       <c r="E77">
-        <v>-10.39715650309237</v>
+        <v>-6.838500488904693</v>
       </c>
       <c r="F77">
-        <v>-1.125266852721398</v>
+        <v>0.402313877637531</v>
       </c>
       <c r="G77">
-        <v>-6.691256208287028</v>
+        <v>-3.559638664623635</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.3958635728743828</v>
       </c>
       <c r="E78">
-        <v>-10.91845178848534</v>
+        <v>-8.170437906410736</v>
       </c>
       <c r="F78">
-        <v>-1.088088066948951</v>
+        <v>0.06468292140009164</v>
       </c>
       <c r="G78">
-        <v>-6.637358862951589</v>
+        <v>-3.61651207791349</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.3101515544020386</v>
       </c>
       <c r="E79">
-        <v>-11.29827754587869</v>
+        <v>-8.361018735023544</v>
       </c>
       <c r="F79">
-        <v>-1.086899359725934</v>
+        <v>-0.2446195263964102</v>
       </c>
       <c r="G79">
-        <v>-6.089529392608259</v>
+        <v>-3.708829246488467</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.2275949118737657</v>
       </c>
       <c r="E80">
-        <v>-12.88391819119046</v>
+        <v>-8.875842831059556</v>
       </c>
       <c r="F80">
-        <v>-1.237097280466734</v>
+        <v>-0.01712664330038753</v>
       </c>
       <c r="G80">
-        <v>-6.116458377946621</v>
+        <v>-2.922202314713429</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.1479216348012617</v>
       </c>
       <c r="E81">
-        <v>-12.34709929689919</v>
+        <v>-9.036839138980254</v>
       </c>
       <c r="F81">
-        <v>-1.205647483652048</v>
+        <v>-0.4252715463337319</v>
       </c>
       <c r="G81">
-        <v>-6.079731665031757</v>
+        <v>-3.857783580401019</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.07042695196642822</v>
       </c>
       <c r="E82">
-        <v>-13.19324919370641</v>
+        <v>-9.864200397129643</v>
       </c>
       <c r="F82">
-        <v>-1.404366196644427</v>
+        <v>-0.2962632637565425</v>
       </c>
       <c r="G82">
-        <v>-5.573357147870452</v>
+        <v>-2.723868877552793</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.006006843686955562</v>
       </c>
       <c r="E83">
-        <v>-13.76181269079144</v>
+        <v>-11.51406386081819</v>
       </c>
       <c r="F83">
-        <v>-1.530676486590699</v>
+        <v>-0.2058577305172129</v>
       </c>
       <c r="G83">
-        <v>-6.097289481596346</v>
+        <v>-3.237947702935675</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.0830636992468934</v>
       </c>
       <c r="E84">
-        <v>-15.12543131245515</v>
+        <v>-11.39058596005104</v>
       </c>
       <c r="F84">
-        <v>-1.458799047049786</v>
+        <v>-0.29250164738043</v>
       </c>
       <c r="G84">
-        <v>-6.029335383100245</v>
+        <v>-2.754823921744594</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.1635612550074459</v>
       </c>
       <c r="E85">
-        <v>-15.88650929655427</v>
+        <v>-12.34113076815708</v>
       </c>
       <c r="F85">
-        <v>-1.669872031487516</v>
+        <v>-0.1473509692248866</v>
       </c>
       <c r="G85">
-        <v>-5.943593782530396</v>
+        <v>-2.62644612823132</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.2511787552476607</v>
       </c>
       <c r="E86">
-        <v>-16.85430759062953</v>
+        <v>-14.007151827105</v>
       </c>
       <c r="F86">
-        <v>-1.603677192329808</v>
+        <v>-0.6148533668732324</v>
       </c>
       <c r="G86">
-        <v>-5.454307867250678</v>
+        <v>-2.261462729288046</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3506460404400529</v>
       </c>
       <c r="E87">
-        <v>-18.07843109896096</v>
+        <v>-14.73103745417912</v>
       </c>
       <c r="F87">
-        <v>-1.722007819084912</v>
+        <v>-0.4361902570700322</v>
       </c>
       <c r="G87">
-        <v>-5.309409123185599</v>
+        <v>-2.927626173951191</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.4682628776534717</v>
       </c>
       <c r="E88">
-        <v>-19.09887290337539</v>
+        <v>-16.63433243723293</v>
       </c>
       <c r="F88">
-        <v>-1.784964570065077</v>
+        <v>-0.4185021279180544</v>
       </c>
       <c r="G88">
-        <v>-5.462307485412604</v>
+        <v>-2.706681839024422</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.6108325066586786</v>
       </c>
       <c r="E89">
-        <v>-20.50297155419366</v>
+        <v>-19.12243908211131</v>
       </c>
       <c r="F89">
-        <v>-2.160126368221154</v>
+        <v>-0.4508374494863331</v>
       </c>
       <c r="G89">
-        <v>-5.515197495729294</v>
+        <v>-2.123014866808836</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.7825521664626028</v>
       </c>
       <c r="E90">
-        <v>-22.17364788442146</v>
+        <v>-18.95854907929971</v>
       </c>
       <c r="F90">
-        <v>-1.819823098742283</v>
+        <v>-0.02490832668228609</v>
       </c>
       <c r="G90">
-        <v>-5.75997334284231</v>
+        <v>-3.245051547611872</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.9843424473457209</v>
       </c>
       <c r="E91">
-        <v>-23.79715562938537</v>
+        <v>-20.03899769278978</v>
       </c>
       <c r="F91">
-        <v>-1.823213606521941</v>
+        <v>-0.6850260262991841</v>
       </c>
       <c r="G91">
-        <v>-5.13325674376681</v>
+        <v>-2.818896335135871</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.210801436883807</v>
       </c>
       <c r="E92">
-        <v>-26.02260172487084</v>
+        <v>-23.25802721335019</v>
       </c>
       <c r="F92">
-        <v>-1.932712180028397</v>
+        <v>-0.9034847345002753</v>
       </c>
       <c r="G92">
-        <v>-5.766240476020849</v>
+        <v>-2.172643342895437</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.452131943634208</v>
       </c>
       <c r="E93">
-        <v>-27.6270083664704</v>
+        <v>-26.27275915752856</v>
       </c>
       <c r="F93">
-        <v>-2.279427841572338</v>
+        <v>-0.7488741006047616</v>
       </c>
       <c r="G93">
-        <v>-5.512953140182633</v>
+        <v>-2.968913784833684</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.694207849497758</v>
       </c>
       <c r="E94">
-        <v>-29.34047877607068</v>
+        <v>-28.7362309038052</v>
       </c>
       <c r="F94">
-        <v>-2.048049915357186</v>
+        <v>-0.7581369049028657</v>
       </c>
       <c r="G94">
-        <v>-5.910975159007956</v>
+        <v>-2.657502890291464</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.922276326954567</v>
       </c>
       <c r="E95">
-        <v>-31.49827173411857</v>
+        <v>-31.67780535038966</v>
       </c>
       <c r="F95">
-        <v>-1.921189589455456</v>
+        <v>-1.087805593664596</v>
       </c>
       <c r="G95">
-        <v>-6.121898643292181</v>
+        <v>-3.434118815088637</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.120342798318021</v>
       </c>
       <c r="E96">
-        <v>-33.85060340706196</v>
+        <v>-32.96130168143566</v>
       </c>
       <c r="F96">
-        <v>-2.08705939308982</v>
+        <v>-1.23594502140944</v>
       </c>
       <c r="G96">
-        <v>-5.792496810939526</v>
+        <v>-3.452798809426555</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.278697369661195</v>
       </c>
       <c r="E97">
-        <v>-36.09801939419565</v>
+        <v>-35.13693456283676</v>
       </c>
       <c r="F97">
-        <v>-2.095367089772497</v>
+        <v>-1.418380516364989</v>
       </c>
       <c r="G97">
-        <v>-6.275696060226474</v>
+        <v>-3.696780600922186</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.391044687671497</v>
       </c>
       <c r="E98">
-        <v>-38.9493232399112</v>
+        <v>-37.81296835055944</v>
       </c>
       <c r="F98">
-        <v>-1.959560395920531</v>
+        <v>-1.14818777875686</v>
       </c>
       <c r="G98">
-        <v>-6.596901401123636</v>
+        <v>-3.477099536295803</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.46339808245975</v>
       </c>
       <c r="E99">
-        <v>-40.94870564869677</v>
+        <v>-40.56633941738512</v>
       </c>
       <c r="F99">
-        <v>-2.322829323274616</v>
+        <v>-1.560414876351201</v>
       </c>
       <c r="G99">
-        <v>-6.749901481218983</v>
+        <v>-4.062138059123236</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.495450031605841</v>
       </c>
       <c r="E100">
-        <v>-44.26324974302697</v>
+        <v>-43.06144708307934</v>
       </c>
       <c r="F100">
-        <v>-2.305388875976075</v>
+        <v>-1.551085802660873</v>
       </c>
       <c r="G100">
-        <v>-7.187222690661775</v>
+        <v>-3.925045341148077</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.501197134499954</v>
       </c>
       <c r="E101">
-        <v>-46.37526435733131</v>
+        <v>-45.79449209432159</v>
       </c>
       <c r="F101">
-        <v>-2.037769875888444</v>
+        <v>-1.662129281373549</v>
       </c>
       <c r="G101">
-        <v>-7.133141596919008</v>
+        <v>-5.007904236531344</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.473100062000092</v>
       </c>
       <c r="E102">
-        <v>-49.13768897581682</v>
+        <v>-48.92063468815518</v>
       </c>
       <c r="F102">
-        <v>-2.09586245347937</v>
+        <v>-1.782922644417176</v>
       </c>
       <c r="G102">
-        <v>-7.752711695438037</v>
+        <v>-4.218416079556469</v>
       </c>
     </row>
   </sheetData>
